--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
@@ -428,7 +428,7 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006054323574062436</v>
+        <v>0.005938928864197806</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +436,7 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009174558939412236</v>
+        <v>0.009846623535268009</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001086816724855453</v>
+        <v>0.01931530268280767</v>
       </c>
     </row>
     <row r="5">
@@ -452,7 +452,7 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009557958575896919</v>
+        <v>0.01813571567763574</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +460,7 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001279820860363543</v>
+        <v>0.009711761478683911</v>
       </c>
     </row>
     <row r="7">
@@ -468,7 +468,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001389241713332012</v>
+        <v>0.7407619747845456</v>
       </c>
     </row>
     <row r="8">
@@ -476,7 +476,7 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001554793273098767</v>
+        <v>0.2382462540845154</v>
       </c>
     </row>
     <row r="9">
@@ -484,7 +484,7 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008581373360939323</v>
+        <v>0.1856680965283886</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004815149211790413</v>
+        <v>0.1421702865808038</v>
       </c>
     </row>
     <row r="11">
@@ -500,7 +500,7 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02925027849152684</v>
+        <v>0.4978147486690432</v>
       </c>
     </row>
     <row r="12">
@@ -508,7 +508,7 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.04191397129325196</v>
+        <v>0.9682289678009692</v>
       </c>
     </row>
     <row r="13">
@@ -516,7 +516,7 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03642623257124797</v>
+        <v>1.985981992290472</v>
       </c>
     </row>
     <row r="14">
@@ -524,7 +524,7 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0622584304830525</v>
+        <v>1.439558576080599</v>
       </c>
     </row>
     <row r="15">
@@ -532,7 +532,7 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05924656424671412</v>
+        <v>3.37900313396065</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +540,7 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1250903106364422</v>
+        <v>2.136224902730901</v>
       </c>
     </row>
     <row r="17">
@@ -548,7 +548,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3328927033010405</v>
+        <v>2.246386806113878</v>
       </c>
     </row>
     <row r="18">
@@ -556,7 +556,7 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1805965351569466</v>
+        <v>1.585081056642812</v>
       </c>
     </row>
     <row r="19">
@@ -564,7 +564,7 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3067258298373781</v>
+        <v>3.055424458911875</v>
       </c>
     </row>
     <row r="20">
@@ -572,7 +572,7 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4095988366892561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -580,7 +580,7 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4508050816087052</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,13 +422,29 @@
           <t>gdpa-mapping</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pd-mapping</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bf-mapping</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.005938928864197806</v>
+        <v>0.006773455198854208</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0002346067002508789</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09004018284380436</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009846623535268009</v>
+        <v>0.01102443625219166</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0002233224608062301</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08325667172670365</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01931530268280767</v>
+        <v>0.02019680206663907</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0002198374214640353</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0936452704668045</v>
       </c>
     </row>
     <row r="5">
@@ -452,7 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01813571567763574</v>
+        <v>0.02191899425524753</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0002583674811467063</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3905089699476957</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009711761478683911</v>
+        <v>0.01130757530161645</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0002398207994701806</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1161556181311607</v>
       </c>
     </row>
     <row r="7">
@@ -468,7 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7407619747845456</v>
+        <v>0.7309687991568353</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0002482990793942008</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1060764088481665</v>
       </c>
     </row>
     <row r="8">
@@ -476,7 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2382462540845154</v>
+        <v>0.2387035070499405</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00026259494072292</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.118406218290329</v>
       </c>
     </row>
     <row r="9">
@@ -484,7 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1856680965283886</v>
+        <v>0.1932330543367425</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0002549292400362901</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1243297706544399</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1421702865808038</v>
+        <v>0.1436601190449437</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0002572949984460138</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1256025222688913</v>
       </c>
     </row>
     <row r="11">
@@ -500,7 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4978147486690432</v>
+        <v>0.5242398428329034</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0002524150002864189</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1391942290961742</v>
       </c>
     </row>
     <row r="12">
@@ -508,7 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9682289678009692</v>
+        <v>0.9649744206608739</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0002364858410146553</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2011694866418839</v>
       </c>
     </row>
     <row r="13">
@@ -516,7 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>1.985981992290472</v>
+        <v>1.934200369498576</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.000226030878839083</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3628069924563169</v>
       </c>
     </row>
     <row r="14">
@@ -524,7 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>1.439558576080599</v>
+        <v>1.385668231431046</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0002153740992071107</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.6231039525568485</v>
       </c>
     </row>
     <row r="15">
@@ -532,7 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>3.37900313396065</v>
+        <v>3.354123516320251</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0002367641999444459</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4786660199612379</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>2.136224902730901</v>
+        <v>2.164730635307496</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0002171391386946198</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6647965600341559</v>
       </c>
     </row>
     <row r="17">
@@ -548,7 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>2.246386806113878</v>
+        <v>2.383027762428392</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0001774416991975159</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.176073047965765</v>
       </c>
     </row>
     <row r="18">
@@ -556,7 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>1.585081056642812</v>
+        <v>1.576749908485217</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0001898800606431905</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9987174089252949</v>
       </c>
     </row>
     <row r="19">
@@ -564,7 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>3.055424458911875</v>
+        <v>2.993068323401967</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0001892883988330141</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.39470680296421</v>
       </c>
     </row>
     <row r="20">
@@ -572,7 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>29.17709230901091</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0001602374792855699</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.101255769357085</v>
       </c>
     </row>
     <row r="21">
@@ -580,7 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4.055745761680883</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0001528908194450196</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.555571509897709</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
+++ b/workspace/framework_paper/fp-mapping-only/gradient_fp_mapping_only_validation_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006252575380494819</v>
+        <v>0.001258258013403974</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002279492001980543</v>
+        <v>0.0002614920005726162</v>
       </c>
       <c r="D2" t="n">
-        <v>0.092201858907938</v>
+        <v>0.08048636548221111</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001014133357093669</v>
+        <v>0.001050899999099784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000230969201948028</v>
+        <v>0.0002747920024557971</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08422518424689769</v>
+        <v>0.08032673597335815</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009114689179114066</v>
+        <v>0.003038402030360885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002485366616747342</v>
+        <v>0.0002887600005487911</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09455914877355098</v>
+        <v>0.08490353584289551</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01449597523198463</v>
+        <v>0.005210783996153623</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000246359997545369</v>
+        <v>0.0002701000004890375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3895223701745272</v>
+        <v>0.3358954062312842</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00137615006766282</v>
+        <v>0.01246302026615012</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000248853359662462</v>
+        <v>0.0002973819976614322</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1134350255131722</v>
+        <v>0.103251870945096</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.007215354224317707</v>
+        <v>0.01378971213649493</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002748499985318631</v>
+        <v>0.0002975459984736517</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1077533359080553</v>
+        <v>0.09496413595974446</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.165597894450766</v>
+        <v>0.1198668466042727</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0002466241788351908</v>
+        <v>0.000283717998827342</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1157332447171211</v>
+        <v>0.1014819601923227</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.158242783548194</v>
+        <v>0.02720987951441202</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002573241791105829</v>
+        <v>0.0002813460008474067</v>
       </c>
       <c r="D9" t="n">
-        <v>2.775828221812844</v>
+        <v>2.517015041783452</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>3.31854769364465</v>
+        <v>0.0902724232559558</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002817800210323185</v>
+        <v>0.0002981960022589192</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1303619668632746</v>
+        <v>0.1113094333559275</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2148393477243371</v>
+        <v>0.1253225318761542</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00027110998169519</v>
+        <v>0.0003525179994176142</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1366257154196501</v>
+        <v>0.1259386099874973</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2925522100128001</v>
+        <v>0.1306457152718213</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0002328008599579334</v>
+        <v>0.0002743399998871609</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1922140652686357</v>
+        <v>0.1841822070628405</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5125659453088883</v>
+        <v>0.1633703565166797</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002243759602424689</v>
+        <v>0.000277763999911258</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3550177922099829</v>
+        <v>0.3271020086109638</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4519910648243968</v>
+        <v>0.890191374673741</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002119517183746211</v>
+        <v>0.0002395740016072523</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6197404824197292</v>
+        <v>0.5717695520073175</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.6693310198537074</v>
+        <v>0.6647566387290135</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0002383292399463244</v>
+        <v>0.0002747959991393145</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6092948831617833</v>
+        <v>0.556775731369853</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4200918654818088</v>
+        <v>4.363696822750499</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0002191199810476974</v>
+        <v>0.0002476440015016124</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6783947517722845</v>
+        <v>0.6311279743909836</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>1.788585313773947</v>
+        <v>2.065047395472648</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001644398990902118</v>
+        <v>0.0002433159972133581</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10608590118587</v>
+        <v>1.459729613810778</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>1.277850377316354</v>
+        <v>3.440792275746353</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0002125391803565435</v>
+        <v>0.0002924739993613912</v>
       </c>
       <c r="D18" t="n">
-        <v>1.010442389696836</v>
+        <v>1.344184317439794</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8695483423257246</v>
+        <v>4.402641219709767</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001897166011622176</v>
+        <v>0.000259379999988596</v>
       </c>
       <c r="D19" t="n">
-        <v>2.324341073334217</v>
+        <v>3.363941842392087</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5669690346042625</v>
+        <v>1.613158587072976</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001690133978263475</v>
+        <v>0.0002500720012176316</v>
       </c>
       <c r="D20" t="n">
-        <v>3.15198868483305</v>
+        <v>4.640929069817066</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>2.231308807905298</v>
+        <v>0.9367982407379896</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001585276005789638</v>
+        <v>0.0001933120007743128</v>
       </c>
       <c r="D21" t="n">
-        <v>4.019970968663692</v>
+        <v>4.02085522390902</v>
       </c>
     </row>
   </sheetData>
